--- a/Opptaksområder/KLASS TSB/OPPTAK_TSB_2016.xlsx
+++ b/Opptaksområder/KLASS TSB/OPPTAK_TSB_2016.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="588">
   <si>
     <t xml:space="preserve">KOMMUNE</t>
   </si>
@@ -161,1639 +161,1621 @@
     <t xml:space="preserve">0235</t>
   </si>
   <si>
+    <t xml:space="preserve">0237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">993467049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSLO UNIVERSITETSSYKEHUS HF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">965985166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOVISENBERG DIAKONALE SYKEHUS AS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">982791952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIAKONHJEMMET SYKEHUS AS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">983971709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYKEHUSET INNLANDET HF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0420</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0520</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0620</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">983975259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYKEHUSET I VESTFOLD HF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0720</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">983975267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYKEHUSET TELEMARK HF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0830</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">983975240</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SØRLANDET SYKEHUS HF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0940</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">983974678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HELSE STAVANGER HF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">983658725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HELSE VEST RHF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">983974694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HELSE FONNA HF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">983974724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HELSE BERGEN HF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">983974732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HELSE FØRDE HF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1420</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">997005562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HELSE MØRE OG ROMSDAL HF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">983658776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HELSE MIDT-NORGE RHF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1520</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">883974832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST OLAVS HOSPITAL HF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1620</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1630</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">983974791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HELSE NORD-TRØNDELAG HF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1640</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1740</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">983974910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORDLANDSSYKEHUSET HF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">883658752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HELSE NORD RHF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">983974899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIVERSITETSSYKEHUSET NORD-NORGE HF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">983974929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HELGELANDSSYKEHUSET HF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1820</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1840</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1850</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1870</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1920</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1940</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">983974880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINNMARKSSYKEHUSET HF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9419</t>
+  </si>
+  <si>
     <t xml:space="preserve">0236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">993467049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OSLO UNIVERSITETSSYKEHUS HF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">965985166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOVISENBERG DIAKONALE SYKEHUS AS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">982791952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIAKONHJEMMET SYKEHUS AS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">983971709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SYKEHUSET INNLANDET HF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0420</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0430</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0520</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0620</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">983975259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SYKEHUSET I VESTFOLD HF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0720</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">983975267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SYKEHUSET TELEMARK HF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0830</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">983975240</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SØRLANDET SYKEHUS HF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0940</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">983974678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HELSE STAVANGER HF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">983658725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HELSE VEST RHF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">983974694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HELSE FONNA HF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">983974724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HELSE BERGEN HF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1260</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">983974732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HELSE FØRDE HF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1420</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1430</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">997005562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HELSE MØRE OG ROMSDAL HF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">983658776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HELSE MIDT-NORGE RHF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1520</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">883974832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ST OLAVS HOSPITAL HF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1620</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1630</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">983974791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HELSE NORD-TRØNDELAG HF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1640</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1740</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1750</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">983974910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORDLANDSSYKEHUSET HF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">883658752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HELSE NORD RHF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">983974899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIVERSITETSSYKEHUSET NORD-NORGE HF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">983974929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HELGELANDSSYKEHUSET HF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1820</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1840</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1850</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1870</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1920</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1940</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">983974880</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FINNMARKSSYKEHUSET HF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9419</t>
   </si>
 </sst>
 </file>
@@ -2450,10 +2432,10 @@
         <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D20" t="s">
         <v>8</v>
@@ -2807,10 +2789,10 @@
         <v>52</v>
       </c>
       <c r="B41" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="C41" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="D41" t="s">
         <v>8</v>
@@ -2821,13 +2803,13 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B42" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C42" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D42" t="s">
         <v>8</v>
@@ -2838,13 +2820,13 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B43" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C43" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D43" t="s">
         <v>8</v>
@@ -2855,13 +2837,13 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B44" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="D44" t="s">
         <v>8</v>
@@ -2872,13 +2854,13 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B45" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="C45" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="D45" t="s">
         <v>8</v>
@@ -2889,13 +2871,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
+        <v>62</v>
+      </c>
+      <c r="B46" t="s">
         <v>60</v>
       </c>
-      <c r="B46" t="s">
-        <v>17</v>
-      </c>
       <c r="C46" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="D46" t="s">
         <v>8</v>
@@ -2906,13 +2888,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>63</v>
+      </c>
+      <c r="B47" t="s">
+        <v>60</v>
+      </c>
+      <c r="C47" t="s">
         <v>61</v>
-      </c>
-      <c r="B47" t="s">
-        <v>62</v>
-      </c>
-      <c r="C47" t="s">
-        <v>63</v>
       </c>
       <c r="D47" t="s">
         <v>8</v>
@@ -2926,10 +2908,10 @@
         <v>64</v>
       </c>
       <c r="B48" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C48" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D48" t="s">
         <v>8</v>
@@ -2943,10 +2925,10 @@
         <v>65</v>
       </c>
       <c r="B49" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C49" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D49" t="s">
         <v>8</v>
@@ -2960,10 +2942,10 @@
         <v>66</v>
       </c>
       <c r="B50" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C50" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D50" t="s">
         <v>8</v>
@@ -2977,10 +2959,10 @@
         <v>67</v>
       </c>
       <c r="B51" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="C51" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="D51" t="s">
         <v>8</v>
@@ -2994,10 +2976,10 @@
         <v>68</v>
       </c>
       <c r="B52" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="C52" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="D52" t="s">
         <v>8</v>
@@ -3011,10 +2993,10 @@
         <v>69</v>
       </c>
       <c r="B53" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="C53" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="D53" t="s">
         <v>8</v>
@@ -3028,10 +3010,10 @@
         <v>70</v>
       </c>
       <c r="B54" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="C54" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="D54" t="s">
         <v>8</v>
@@ -3045,10 +3027,10 @@
         <v>71</v>
       </c>
       <c r="B55" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C55" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D55" t="s">
         <v>8</v>
@@ -3062,10 +3044,10 @@
         <v>72</v>
       </c>
       <c r="B56" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C56" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D56" t="s">
         <v>8</v>
@@ -3079,10 +3061,10 @@
         <v>73</v>
       </c>
       <c r="B57" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C57" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D57" t="s">
         <v>8</v>
@@ -3096,10 +3078,10 @@
         <v>74</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C58" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D58" t="s">
         <v>8</v>
@@ -3113,10 +3095,10 @@
         <v>75</v>
       </c>
       <c r="B59" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C59" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D59" t="s">
         <v>8</v>
@@ -3130,10 +3112,10 @@
         <v>76</v>
       </c>
       <c r="B60" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C60" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D60" t="s">
         <v>8</v>
@@ -3147,10 +3129,10 @@
         <v>77</v>
       </c>
       <c r="B61" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C61" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D61" t="s">
         <v>8</v>
@@ -3164,10 +3146,10 @@
         <v>78</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C62" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D62" t="s">
         <v>8</v>
@@ -3181,10 +3163,10 @@
         <v>79</v>
       </c>
       <c r="B63" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C63" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D63" t="s">
         <v>8</v>
@@ -3198,10 +3180,10 @@
         <v>80</v>
       </c>
       <c r="B64" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C64" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D64" t="s">
         <v>8</v>
@@ -3215,10 +3197,10 @@
         <v>81</v>
       </c>
       <c r="B65" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C65" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D65" t="s">
         <v>8</v>
@@ -3232,10 +3214,10 @@
         <v>82</v>
       </c>
       <c r="B66" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C66" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D66" t="s">
         <v>8</v>
@@ -3249,10 +3231,10 @@
         <v>83</v>
       </c>
       <c r="B67" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C67" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D67" t="s">
         <v>8</v>
@@ -3266,10 +3248,10 @@
         <v>84</v>
       </c>
       <c r="B68" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C68" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D68" t="s">
         <v>8</v>
@@ -3283,10 +3265,10 @@
         <v>85</v>
       </c>
       <c r="B69" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C69" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D69" t="s">
         <v>8</v>
@@ -3300,10 +3282,10 @@
         <v>86</v>
       </c>
       <c r="B70" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C70" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D70" t="s">
         <v>8</v>
@@ -3317,10 +3299,10 @@
         <v>87</v>
       </c>
       <c r="B71" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C71" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D71" t="s">
         <v>8</v>
@@ -3334,10 +3316,10 @@
         <v>88</v>
       </c>
       <c r="B72" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C72" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D72" t="s">
         <v>8</v>
@@ -3351,10 +3333,10 @@
         <v>89</v>
       </c>
       <c r="B73" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C73" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D73" t="s">
         <v>8</v>
@@ -3368,10 +3350,10 @@
         <v>90</v>
       </c>
       <c r="B74" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C74" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D74" t="s">
         <v>8</v>
@@ -3385,10 +3367,10 @@
         <v>91</v>
       </c>
       <c r="B75" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C75" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D75" t="s">
         <v>8</v>
@@ -3402,10 +3384,10 @@
         <v>92</v>
       </c>
       <c r="B76" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C76" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D76" t="s">
         <v>8</v>
@@ -3419,10 +3401,10 @@
         <v>93</v>
       </c>
       <c r="B77" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C77" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D77" t="s">
         <v>8</v>
@@ -3436,10 +3418,10 @@
         <v>94</v>
       </c>
       <c r="B78" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C78" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D78" t="s">
         <v>8</v>
@@ -3453,10 +3435,10 @@
         <v>95</v>
       </c>
       <c r="B79" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C79" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D79" t="s">
         <v>8</v>
@@ -3470,10 +3452,10 @@
         <v>96</v>
       </c>
       <c r="B80" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C80" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D80" t="s">
         <v>8</v>
@@ -3487,10 +3469,10 @@
         <v>97</v>
       </c>
       <c r="B81" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C81" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D81" t="s">
         <v>8</v>
@@ -3504,10 +3486,10 @@
         <v>98</v>
       </c>
       <c r="B82" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="C82" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="D82" t="s">
         <v>8</v>
@@ -3521,10 +3503,10 @@
         <v>99</v>
       </c>
       <c r="B83" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="C83" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="D83" t="s">
         <v>8</v>
@@ -3538,10 +3520,10 @@
         <v>100</v>
       </c>
       <c r="B84" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C84" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D84" t="s">
         <v>8</v>
@@ -3555,10 +3537,10 @@
         <v>101</v>
       </c>
       <c r="B85" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C85" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D85" t="s">
         <v>8</v>
@@ -3572,10 +3554,10 @@
         <v>102</v>
       </c>
       <c r="B86" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C86" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D86" t="s">
         <v>8</v>
@@ -3589,10 +3571,10 @@
         <v>103</v>
       </c>
       <c r="B87" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C87" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D87" t="s">
         <v>8</v>
@@ -3606,10 +3588,10 @@
         <v>104</v>
       </c>
       <c r="B88" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C88" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D88" t="s">
         <v>8</v>
@@ -3623,10 +3605,10 @@
         <v>105</v>
       </c>
       <c r="B89" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C89" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D89" t="s">
         <v>8</v>
@@ -3640,10 +3622,10 @@
         <v>106</v>
       </c>
       <c r="B90" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C90" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D90" t="s">
         <v>8</v>
@@ -3657,10 +3639,10 @@
         <v>107</v>
       </c>
       <c r="B91" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C91" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D91" t="s">
         <v>8</v>
@@ -3674,10 +3656,10 @@
         <v>108</v>
       </c>
       <c r="B92" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C92" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D92" t="s">
         <v>8</v>
@@ -3691,10 +3673,10 @@
         <v>109</v>
       </c>
       <c r="B93" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="C93" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="D93" t="s">
         <v>8</v>
@@ -4048,10 +4030,10 @@
         <v>130</v>
       </c>
       <c r="B114" t="s">
-        <v>36</v>
+        <v>131</v>
       </c>
       <c r="C114" t="s">
-        <v>37</v>
+        <v>132</v>
       </c>
       <c r="D114" t="s">
         <v>8</v>
@@ -4062,13 +4044,13 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
+        <v>133</v>
+      </c>
+      <c r="B115" t="s">
         <v>131</v>
       </c>
-      <c r="B115" t="s">
+      <c r="C115" t="s">
         <v>132</v>
-      </c>
-      <c r="C115" t="s">
-        <v>133</v>
       </c>
       <c r="D115" t="s">
         <v>8</v>
@@ -4082,10 +4064,10 @@
         <v>134</v>
       </c>
       <c r="B116" t="s">
+        <v>131</v>
+      </c>
+      <c r="C116" t="s">
         <v>132</v>
-      </c>
-      <c r="C116" t="s">
-        <v>133</v>
       </c>
       <c r="D116" t="s">
         <v>8</v>
@@ -4099,10 +4081,10 @@
         <v>135</v>
       </c>
       <c r="B117" t="s">
+        <v>131</v>
+      </c>
+      <c r="C117" t="s">
         <v>132</v>
-      </c>
-      <c r="C117" t="s">
-        <v>133</v>
       </c>
       <c r="D117" t="s">
         <v>8</v>
@@ -4116,10 +4098,10 @@
         <v>136</v>
       </c>
       <c r="B118" t="s">
+        <v>131</v>
+      </c>
+      <c r="C118" t="s">
         <v>132</v>
-      </c>
-      <c r="C118" t="s">
-        <v>133</v>
       </c>
       <c r="D118" t="s">
         <v>8</v>
@@ -4133,10 +4115,10 @@
         <v>137</v>
       </c>
       <c r="B119" t="s">
-        <v>132</v>
+        <v>36</v>
       </c>
       <c r="C119" t="s">
-        <v>133</v>
+        <v>37</v>
       </c>
       <c r="D119" t="s">
         <v>8</v>
@@ -4167,10 +4149,10 @@
         <v>139</v>
       </c>
       <c r="B121" t="s">
-        <v>36</v>
+        <v>131</v>
       </c>
       <c r="C121" t="s">
-        <v>37</v>
+        <v>132</v>
       </c>
       <c r="D121" t="s">
         <v>8</v>
@@ -4184,10 +4166,10 @@
         <v>140</v>
       </c>
       <c r="B122" t="s">
+        <v>131</v>
+      </c>
+      <c r="C122" t="s">
         <v>132</v>
-      </c>
-      <c r="C122" t="s">
-        <v>133</v>
       </c>
       <c r="D122" t="s">
         <v>8</v>
@@ -4201,10 +4183,10 @@
         <v>141</v>
       </c>
       <c r="B123" t="s">
+        <v>131</v>
+      </c>
+      <c r="C123" t="s">
         <v>132</v>
-      </c>
-      <c r="C123" t="s">
-        <v>133</v>
       </c>
       <c r="D123" t="s">
         <v>8</v>
@@ -4218,10 +4200,10 @@
         <v>142</v>
       </c>
       <c r="B124" t="s">
+        <v>131</v>
+      </c>
+      <c r="C124" t="s">
         <v>132</v>
-      </c>
-      <c r="C124" t="s">
-        <v>133</v>
       </c>
       <c r="D124" t="s">
         <v>8</v>
@@ -4235,10 +4217,10 @@
         <v>143</v>
       </c>
       <c r="B125" t="s">
+        <v>131</v>
+      </c>
+      <c r="C125" t="s">
         <v>132</v>
-      </c>
-      <c r="C125" t="s">
-        <v>133</v>
       </c>
       <c r="D125" t="s">
         <v>8</v>
@@ -4252,10 +4234,10 @@
         <v>144</v>
       </c>
       <c r="B126" t="s">
+        <v>131</v>
+      </c>
+      <c r="C126" t="s">
         <v>132</v>
-      </c>
-      <c r="C126" t="s">
-        <v>133</v>
       </c>
       <c r="D126" t="s">
         <v>8</v>
@@ -4269,10 +4251,10 @@
         <v>145</v>
       </c>
       <c r="B127" t="s">
+        <v>131</v>
+      </c>
+      <c r="C127" t="s">
         <v>132</v>
-      </c>
-      <c r="C127" t="s">
-        <v>133</v>
       </c>
       <c r="D127" t="s">
         <v>8</v>
@@ -4286,10 +4268,10 @@
         <v>146</v>
       </c>
       <c r="B128" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="C128" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="D128" t="s">
         <v>8</v>
@@ -4300,13 +4282,13 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
+        <v>149</v>
+      </c>
+      <c r="B129" t="s">
         <v>147</v>
       </c>
-      <c r="B129" t="s">
+      <c r="C129" t="s">
         <v>148</v>
-      </c>
-      <c r="C129" t="s">
-        <v>149</v>
       </c>
       <c r="D129" t="s">
         <v>8</v>
@@ -4320,10 +4302,10 @@
         <v>150</v>
       </c>
       <c r="B130" t="s">
+        <v>147</v>
+      </c>
+      <c r="C130" t="s">
         <v>148</v>
-      </c>
-      <c r="C130" t="s">
-        <v>149</v>
       </c>
       <c r="D130" t="s">
         <v>8</v>
@@ -4337,10 +4319,10 @@
         <v>151</v>
       </c>
       <c r="B131" t="s">
+        <v>147</v>
+      </c>
+      <c r="C131" t="s">
         <v>148</v>
-      </c>
-      <c r="C131" t="s">
-        <v>149</v>
       </c>
       <c r="D131" t="s">
         <v>8</v>
@@ -4354,10 +4336,10 @@
         <v>152</v>
       </c>
       <c r="B132" t="s">
+        <v>147</v>
+      </c>
+      <c r="C132" t="s">
         <v>148</v>
-      </c>
-      <c r="C132" t="s">
-        <v>149</v>
       </c>
       <c r="D132" t="s">
         <v>8</v>
@@ -4371,10 +4353,10 @@
         <v>153</v>
       </c>
       <c r="B133" t="s">
+        <v>147</v>
+      </c>
+      <c r="C133" t="s">
         <v>148</v>
-      </c>
-      <c r="C133" t="s">
-        <v>149</v>
       </c>
       <c r="D133" t="s">
         <v>8</v>
@@ -4388,10 +4370,10 @@
         <v>154</v>
       </c>
       <c r="B134" t="s">
+        <v>147</v>
+      </c>
+      <c r="C134" t="s">
         <v>148</v>
-      </c>
-      <c r="C134" t="s">
-        <v>149</v>
       </c>
       <c r="D134" t="s">
         <v>8</v>
@@ -4405,10 +4387,10 @@
         <v>155</v>
       </c>
       <c r="B135" t="s">
+        <v>147</v>
+      </c>
+      <c r="C135" t="s">
         <v>148</v>
-      </c>
-      <c r="C135" t="s">
-        <v>149</v>
       </c>
       <c r="D135" t="s">
         <v>8</v>
@@ -4422,10 +4404,10 @@
         <v>156</v>
       </c>
       <c r="B136" t="s">
+        <v>147</v>
+      </c>
+      <c r="C136" t="s">
         <v>148</v>
-      </c>
-      <c r="C136" t="s">
-        <v>149</v>
       </c>
       <c r="D136" t="s">
         <v>8</v>
@@ -4439,10 +4421,10 @@
         <v>157</v>
       </c>
       <c r="B137" t="s">
+        <v>147</v>
+      </c>
+      <c r="C137" t="s">
         <v>148</v>
-      </c>
-      <c r="C137" t="s">
-        <v>149</v>
       </c>
       <c r="D137" t="s">
         <v>8</v>
@@ -4456,10 +4438,10 @@
         <v>158</v>
       </c>
       <c r="B138" t="s">
+        <v>147</v>
+      </c>
+      <c r="C138" t="s">
         <v>148</v>
-      </c>
-      <c r="C138" t="s">
-        <v>149</v>
       </c>
       <c r="D138" t="s">
         <v>8</v>
@@ -4473,10 +4455,10 @@
         <v>159</v>
       </c>
       <c r="B139" t="s">
+        <v>147</v>
+      </c>
+      <c r="C139" t="s">
         <v>148</v>
-      </c>
-      <c r="C139" t="s">
-        <v>149</v>
       </c>
       <c r="D139" t="s">
         <v>8</v>
@@ -4490,10 +4472,10 @@
         <v>160</v>
       </c>
       <c r="B140" t="s">
+        <v>147</v>
+      </c>
+      <c r="C140" t="s">
         <v>148</v>
-      </c>
-      <c r="C140" t="s">
-        <v>149</v>
       </c>
       <c r="D140" t="s">
         <v>8</v>
@@ -4507,10 +4489,10 @@
         <v>161</v>
       </c>
       <c r="B141" t="s">
+        <v>147</v>
+      </c>
+      <c r="C141" t="s">
         <v>148</v>
-      </c>
-      <c r="C141" t="s">
-        <v>149</v>
       </c>
       <c r="D141" t="s">
         <v>8</v>
@@ -4524,10 +4506,10 @@
         <v>162</v>
       </c>
       <c r="B142" t="s">
+        <v>147</v>
+      </c>
+      <c r="C142" t="s">
         <v>148</v>
-      </c>
-      <c r="C142" t="s">
-        <v>149</v>
       </c>
       <c r="D142" t="s">
         <v>8</v>
@@ -4541,10 +4523,10 @@
         <v>163</v>
       </c>
       <c r="B143" t="s">
+        <v>147</v>
+      </c>
+      <c r="C143" t="s">
         <v>148</v>
-      </c>
-      <c r="C143" t="s">
-        <v>149</v>
       </c>
       <c r="D143" t="s">
         <v>8</v>
@@ -4558,10 +4540,10 @@
         <v>164</v>
       </c>
       <c r="B144" t="s">
+        <v>147</v>
+      </c>
+      <c r="C144" t="s">
         <v>148</v>
-      </c>
-      <c r="C144" t="s">
-        <v>149</v>
       </c>
       <c r="D144" t="s">
         <v>8</v>
@@ -4575,10 +4557,10 @@
         <v>165</v>
       </c>
       <c r="B145" t="s">
+        <v>147</v>
+      </c>
+      <c r="C145" t="s">
         <v>148</v>
-      </c>
-      <c r="C145" t="s">
-        <v>149</v>
       </c>
       <c r="D145" t="s">
         <v>8</v>
@@ -4592,10 +4574,10 @@
         <v>166</v>
       </c>
       <c r="B146" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="C146" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="D146" t="s">
         <v>8</v>
@@ -4606,13 +4588,13 @@
     </row>
     <row r="147">
       <c r="A147" t="s">
+        <v>169</v>
+      </c>
+      <c r="B147" t="s">
         <v>167</v>
       </c>
-      <c r="B147" t="s">
+      <c r="C147" t="s">
         <v>168</v>
-      </c>
-      <c r="C147" t="s">
-        <v>169</v>
       </c>
       <c r="D147" t="s">
         <v>8</v>
@@ -4626,10 +4608,10 @@
         <v>170</v>
       </c>
       <c r="B148" t="s">
+        <v>167</v>
+      </c>
+      <c r="C148" t="s">
         <v>168</v>
-      </c>
-      <c r="C148" t="s">
-        <v>169</v>
       </c>
       <c r="D148" t="s">
         <v>8</v>
@@ -4643,10 +4625,10 @@
         <v>171</v>
       </c>
       <c r="B149" t="s">
+        <v>167</v>
+      </c>
+      <c r="C149" t="s">
         <v>168</v>
-      </c>
-      <c r="C149" t="s">
-        <v>169</v>
       </c>
       <c r="D149" t="s">
         <v>8</v>
@@ -4660,10 +4642,10 @@
         <v>172</v>
       </c>
       <c r="B150" t="s">
+        <v>167</v>
+      </c>
+      <c r="C150" t="s">
         <v>168</v>
-      </c>
-      <c r="C150" t="s">
-        <v>169</v>
       </c>
       <c r="D150" t="s">
         <v>8</v>
@@ -4677,10 +4659,10 @@
         <v>173</v>
       </c>
       <c r="B151" t="s">
+        <v>167</v>
+      </c>
+      <c r="C151" t="s">
         <v>168</v>
-      </c>
-      <c r="C151" t="s">
-        <v>169</v>
       </c>
       <c r="D151" t="s">
         <v>8</v>
@@ -4694,10 +4676,10 @@
         <v>174</v>
       </c>
       <c r="B152" t="s">
+        <v>167</v>
+      </c>
+      <c r="C152" t="s">
         <v>168</v>
-      </c>
-      <c r="C152" t="s">
-        <v>169</v>
       </c>
       <c r="D152" t="s">
         <v>8</v>
@@ -4711,10 +4693,10 @@
         <v>175</v>
       </c>
       <c r="B153" t="s">
+        <v>167</v>
+      </c>
+      <c r="C153" t="s">
         <v>168</v>
-      </c>
-      <c r="C153" t="s">
-        <v>169</v>
       </c>
       <c r="D153" t="s">
         <v>8</v>
@@ -4728,10 +4710,10 @@
         <v>176</v>
       </c>
       <c r="B154" t="s">
+        <v>167</v>
+      </c>
+      <c r="C154" t="s">
         <v>168</v>
-      </c>
-      <c r="C154" t="s">
-        <v>169</v>
       </c>
       <c r="D154" t="s">
         <v>8</v>
@@ -4745,10 +4727,10 @@
         <v>177</v>
       </c>
       <c r="B155" t="s">
+        <v>167</v>
+      </c>
+      <c r="C155" t="s">
         <v>168</v>
-      </c>
-      <c r="C155" t="s">
-        <v>169</v>
       </c>
       <c r="D155" t="s">
         <v>8</v>
@@ -4762,10 +4744,10 @@
         <v>178</v>
       </c>
       <c r="B156" t="s">
+        <v>167</v>
+      </c>
+      <c r="C156" t="s">
         <v>168</v>
-      </c>
-      <c r="C156" t="s">
-        <v>169</v>
       </c>
       <c r="D156" t="s">
         <v>8</v>
@@ -4779,10 +4761,10 @@
         <v>179</v>
       </c>
       <c r="B157" t="s">
+        <v>167</v>
+      </c>
+      <c r="C157" t="s">
         <v>168</v>
-      </c>
-      <c r="C157" t="s">
-        <v>169</v>
       </c>
       <c r="D157" t="s">
         <v>8</v>
@@ -4796,10 +4778,10 @@
         <v>180</v>
       </c>
       <c r="B158" t="s">
+        <v>167</v>
+      </c>
+      <c r="C158" t="s">
         <v>168</v>
-      </c>
-      <c r="C158" t="s">
-        <v>169</v>
       </c>
       <c r="D158" t="s">
         <v>8</v>
@@ -4813,10 +4795,10 @@
         <v>181</v>
       </c>
       <c r="B159" t="s">
+        <v>167</v>
+      </c>
+      <c r="C159" t="s">
         <v>168</v>
-      </c>
-      <c r="C159" t="s">
-        <v>169</v>
       </c>
       <c r="D159" t="s">
         <v>8</v>
@@ -4830,10 +4812,10 @@
         <v>182</v>
       </c>
       <c r="B160" t="s">
+        <v>167</v>
+      </c>
+      <c r="C160" t="s">
         <v>168</v>
-      </c>
-      <c r="C160" t="s">
-        <v>169</v>
       </c>
       <c r="D160" t="s">
         <v>8</v>
@@ -4847,10 +4829,10 @@
         <v>183</v>
       </c>
       <c r="B161" t="s">
+        <v>167</v>
+      </c>
+      <c r="C161" t="s">
         <v>168</v>
-      </c>
-      <c r="C161" t="s">
-        <v>169</v>
       </c>
       <c r="D161" t="s">
         <v>8</v>
@@ -4864,10 +4846,10 @@
         <v>184</v>
       </c>
       <c r="B162" t="s">
+        <v>167</v>
+      </c>
+      <c r="C162" t="s">
         <v>168</v>
-      </c>
-      <c r="C162" t="s">
-        <v>169</v>
       </c>
       <c r="D162" t="s">
         <v>8</v>
@@ -4881,10 +4863,10 @@
         <v>185</v>
       </c>
       <c r="B163" t="s">
+        <v>167</v>
+      </c>
+      <c r="C163" t="s">
         <v>168</v>
-      </c>
-      <c r="C163" t="s">
-        <v>169</v>
       </c>
       <c r="D163" t="s">
         <v>8</v>
@@ -4898,10 +4880,10 @@
         <v>186</v>
       </c>
       <c r="B164" t="s">
+        <v>167</v>
+      </c>
+      <c r="C164" t="s">
         <v>168</v>
-      </c>
-      <c r="C164" t="s">
-        <v>169</v>
       </c>
       <c r="D164" t="s">
         <v>8</v>
@@ -4915,10 +4897,10 @@
         <v>187</v>
       </c>
       <c r="B165" t="s">
-        <v>168</v>
+        <v>6</v>
       </c>
       <c r="C165" t="s">
-        <v>169</v>
+        <v>7</v>
       </c>
       <c r="D165" t="s">
         <v>8</v>
@@ -4932,10 +4914,10 @@
         <v>188</v>
       </c>
       <c r="B166" t="s">
+        <v>167</v>
+      </c>
+      <c r="C166" t="s">
         <v>168</v>
-      </c>
-      <c r="C166" t="s">
-        <v>169</v>
       </c>
       <c r="D166" t="s">
         <v>8</v>
@@ -4949,10 +4931,10 @@
         <v>189</v>
       </c>
       <c r="B167" t="s">
+        <v>167</v>
+      </c>
+      <c r="C167" t="s">
         <v>168</v>
-      </c>
-      <c r="C167" t="s">
-        <v>169</v>
       </c>
       <c r="D167" t="s">
         <v>8</v>
@@ -4966,10 +4948,10 @@
         <v>190</v>
       </c>
       <c r="B168" t="s">
+        <v>167</v>
+      </c>
+      <c r="C168" t="s">
         <v>168</v>
-      </c>
-      <c r="C168" t="s">
-        <v>169</v>
       </c>
       <c r="D168" t="s">
         <v>8</v>
@@ -4983,10 +4965,10 @@
         <v>191</v>
       </c>
       <c r="B169" t="s">
+        <v>167</v>
+      </c>
+      <c r="C169" t="s">
         <v>168</v>
-      </c>
-      <c r="C169" t="s">
-        <v>169</v>
       </c>
       <c r="D169" t="s">
         <v>8</v>
@@ -5000,10 +4982,10 @@
         <v>192</v>
       </c>
       <c r="B170" t="s">
+        <v>167</v>
+      </c>
+      <c r="C170" t="s">
         <v>168</v>
-      </c>
-      <c r="C170" t="s">
-        <v>169</v>
       </c>
       <c r="D170" t="s">
         <v>8</v>
@@ -5017,10 +4999,10 @@
         <v>193</v>
       </c>
       <c r="B171" t="s">
+        <v>167</v>
+      </c>
+      <c r="C171" t="s">
         <v>168</v>
-      </c>
-      <c r="C171" t="s">
-        <v>169</v>
       </c>
       <c r="D171" t="s">
         <v>8</v>
@@ -5034,10 +5016,10 @@
         <v>194</v>
       </c>
       <c r="B172" t="s">
+        <v>167</v>
+      </c>
+      <c r="C172" t="s">
         <v>168</v>
-      </c>
-      <c r="C172" t="s">
-        <v>169</v>
       </c>
       <c r="D172" t="s">
         <v>8</v>
@@ -5051,10 +5033,10 @@
         <v>195</v>
       </c>
       <c r="B173" t="s">
+        <v>167</v>
+      </c>
+      <c r="C173" t="s">
         <v>168</v>
-      </c>
-      <c r="C173" t="s">
-        <v>169</v>
       </c>
       <c r="D173" t="s">
         <v>8</v>
@@ -5068,10 +5050,10 @@
         <v>196</v>
       </c>
       <c r="B174" t="s">
+        <v>167</v>
+      </c>
+      <c r="C174" t="s">
         <v>168</v>
-      </c>
-      <c r="C174" t="s">
-        <v>169</v>
       </c>
       <c r="D174" t="s">
         <v>8</v>
@@ -5085,10 +5067,10 @@
         <v>197</v>
       </c>
       <c r="B175" t="s">
+        <v>167</v>
+      </c>
+      <c r="C175" t="s">
         <v>168</v>
-      </c>
-      <c r="C175" t="s">
-        <v>169</v>
       </c>
       <c r="D175" t="s">
         <v>8</v>
@@ -5102,10 +5084,10 @@
         <v>198</v>
       </c>
       <c r="B176" t="s">
+        <v>167</v>
+      </c>
+      <c r="C176" t="s">
         <v>168</v>
-      </c>
-      <c r="C176" t="s">
-        <v>169</v>
       </c>
       <c r="D176" t="s">
         <v>8</v>
@@ -5745,13 +5727,13 @@
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B214" t="s">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="C214" t="s">
-        <v>233</v>
+        <v>208</v>
       </c>
       <c r="D214" t="s">
         <v>202</v>
@@ -5762,13 +5744,13 @@
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B215" t="s">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="C215" t="s">
-        <v>208</v>
+        <v>233</v>
       </c>
       <c r="D215" t="s">
         <v>202</v>
@@ -5779,7 +5761,7 @@
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B216" t="s">
         <v>232</v>
@@ -5796,7 +5778,7 @@
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B217" t="s">
         <v>232</v>
@@ -5813,7 +5795,7 @@
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B218" t="s">
         <v>232</v>
@@ -5830,7 +5812,7 @@
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B219" t="s">
         <v>232</v>
@@ -5847,7 +5829,7 @@
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B220" t="s">
         <v>232</v>
@@ -5864,7 +5846,7 @@
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B221" t="s">
         <v>232</v>
@@ -5881,7 +5863,7 @@
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B222" t="s">
         <v>232</v>
@@ -5898,7 +5880,7 @@
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B223" t="s">
         <v>232</v>
@@ -5915,7 +5897,7 @@
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B224" t="s">
         <v>232</v>
@@ -5932,7 +5914,7 @@
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B225" t="s">
         <v>232</v>
@@ -5949,7 +5931,7 @@
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B226" t="s">
         <v>232</v>
@@ -5966,7 +5948,7 @@
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B227" t="s">
         <v>232</v>
@@ -5983,7 +5965,7 @@
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B228" t="s">
         <v>232</v>
@@ -6000,7 +5982,7 @@
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B229" t="s">
         <v>232</v>
@@ -6017,7 +5999,7 @@
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B230" t="s">
         <v>232</v>
@@ -6034,7 +6016,7 @@
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B231" t="s">
         <v>232</v>
@@ -6051,7 +6033,7 @@
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B232" t="s">
         <v>232</v>
@@ -6068,7 +6050,7 @@
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B233" t="s">
         <v>232</v>
@@ -6085,7 +6067,7 @@
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B234" t="s">
         <v>232</v>
@@ -6102,7 +6084,7 @@
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B235" t="s">
         <v>232</v>
@@ -6119,13 +6101,13 @@
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B236" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
       <c r="C236" t="s">
-        <v>233</v>
+        <v>268</v>
       </c>
       <c r="D236" t="s">
         <v>202</v>
@@ -6136,13 +6118,13 @@
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B237" t="s">
-        <v>267</v>
+        <v>232</v>
       </c>
       <c r="C237" t="s">
-        <v>268</v>
+        <v>233</v>
       </c>
       <c r="D237" t="s">
         <v>202</v>
@@ -6153,13 +6135,13 @@
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B238" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
       <c r="C238" t="s">
-        <v>233</v>
+        <v>268</v>
       </c>
       <c r="D238" t="s">
         <v>202</v>
@@ -6170,7 +6152,7 @@
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B239" t="s">
         <v>267</v>
@@ -6187,7 +6169,7 @@
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B240" t="s">
         <v>267</v>
@@ -6204,7 +6186,7 @@
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B241" t="s">
         <v>267</v>
@@ -6221,7 +6203,7 @@
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B242" t="s">
         <v>267</v>
@@ -6238,7 +6220,7 @@
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B243" t="s">
         <v>267</v>
@@ -6255,7 +6237,7 @@
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B244" t="s">
         <v>267</v>
@@ -6272,7 +6254,7 @@
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B245" t="s">
         <v>267</v>
@@ -6289,7 +6271,7 @@
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B246" t="s">
         <v>267</v>
@@ -6306,7 +6288,7 @@
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B247" t="s">
         <v>267</v>
@@ -6323,7 +6305,7 @@
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B248" t="s">
         <v>267</v>
@@ -6340,7 +6322,7 @@
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B249" t="s">
         <v>267</v>
@@ -6357,7 +6339,7 @@
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B250" t="s">
         <v>267</v>
@@ -6374,7 +6356,7 @@
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B251" t="s">
         <v>267</v>
@@ -6391,7 +6373,7 @@
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B252" t="s">
         <v>267</v>
@@ -6408,7 +6390,7 @@
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B253" t="s">
         <v>267</v>
@@ -6425,7 +6407,7 @@
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B254" t="s">
         <v>267</v>
@@ -6442,7 +6424,7 @@
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B255" t="s">
         <v>267</v>
@@ -6459,7 +6441,7 @@
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B256" t="s">
         <v>267</v>
@@ -6476,7 +6458,7 @@
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B257" t="s">
         <v>267</v>
@@ -6493,7 +6475,7 @@
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B258" t="s">
         <v>267</v>
@@ -6510,7 +6492,7 @@
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B259" t="s">
         <v>267</v>
@@ -6527,24 +6509,24 @@
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B260" t="s">
-        <v>292</v>
+        <v>267</v>
       </c>
       <c r="C260" t="s">
-        <v>293</v>
+        <v>268</v>
       </c>
       <c r="D260" t="s">
-        <v>294</v>
+        <v>202</v>
       </c>
       <c r="E260" t="s">
-        <v>295</v>
+        <v>203</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B261" t="s">
         <v>267</v>
@@ -6561,636 +6543,636 @@
     </row>
     <row r="262">
       <c r="A262" t="s">
+        <v>294</v>
+      </c>
+      <c r="B262" t="s">
+        <v>295</v>
+      </c>
+      <c r="C262" t="s">
+        <v>296</v>
+      </c>
+      <c r="D262" t="s">
         <v>297</v>
       </c>
-      <c r="B262" t="s">
-        <v>267</v>
-      </c>
-      <c r="C262" t="s">
-        <v>268</v>
-      </c>
-      <c r="D262" t="s">
-        <v>202</v>
-      </c>
       <c r="E262" t="s">
-        <v>203</v>
+        <v>298</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="s">
+        <v>299</v>
+      </c>
+      <c r="B263" t="s">
+        <v>295</v>
+      </c>
+      <c r="C263" t="s">
+        <v>296</v>
+      </c>
+      <c r="D263" t="s">
+        <v>297</v>
+      </c>
+      <c r="E263" t="s">
         <v>298</v>
-      </c>
-      <c r="B263" t="s">
-        <v>292</v>
-      </c>
-      <c r="C263" t="s">
-        <v>293</v>
-      </c>
-      <c r="D263" t="s">
-        <v>294</v>
-      </c>
-      <c r="E263" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B264" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C264" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D264" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E264" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B265" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C265" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D265" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E265" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B266" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C266" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D266" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E266" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B267" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C267" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D267" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E267" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B268" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C268" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D268" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E268" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B269" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C269" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D269" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E269" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B270" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C270" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D270" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E270" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B271" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C271" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D271" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E271" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B272" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C272" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D272" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E272" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B273" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C273" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D273" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E273" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B274" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C274" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D274" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E274" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B275" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C275" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D275" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E275" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B276" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C276" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D276" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E276" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B277" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C277" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D277" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E277" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B278" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C278" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D278" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E278" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B279" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C279" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D279" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E279" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B280" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C280" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D280" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E280" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B281" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C281" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D281" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E281" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B282" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C282" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D282" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E282" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B283" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C283" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D283" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E283" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B284" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C284" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D284" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E284" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B285" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C285" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D285" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E285" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B286" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C286" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D286" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E286" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B287" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C287" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D287" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E287" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B288" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C288" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D288" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E288" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B289" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C289" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D289" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E289" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B290" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C290" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D290" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E290" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B291" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C291" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D291" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E291" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B292" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C292" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D292" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E292" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B293" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C293" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D293" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E293" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B294" t="s">
-        <v>292</v>
+        <v>331</v>
       </c>
       <c r="C294" t="s">
-        <v>293</v>
+        <v>332</v>
       </c>
       <c r="D294" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E294" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B295" t="s">
-        <v>331</v>
+        <v>295</v>
       </c>
       <c r="C295" t="s">
-        <v>332</v>
+        <v>296</v>
       </c>
       <c r="D295" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E295" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B296" t="s">
-        <v>331</v>
+        <v>295</v>
       </c>
       <c r="C296" t="s">
-        <v>332</v>
+        <v>296</v>
       </c>
       <c r="D296" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E296" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B297" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C297" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D297" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E297" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B298" t="s">
-        <v>292</v>
+        <v>331</v>
       </c>
       <c r="C298" t="s">
-        <v>293</v>
+        <v>332</v>
       </c>
       <c r="D298" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E298" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B299" t="s">
         <v>331</v>
@@ -7199,15 +7181,15 @@
         <v>332</v>
       </c>
       <c r="D299" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E299" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B300" t="s">
         <v>331</v>
@@ -7216,15 +7198,15 @@
         <v>332</v>
       </c>
       <c r="D300" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E300" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B301" t="s">
         <v>331</v>
@@ -7233,15 +7215,15 @@
         <v>332</v>
       </c>
       <c r="D301" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E301" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B302" t="s">
         <v>331</v>
@@ -7250,15 +7232,15 @@
         <v>332</v>
       </c>
       <c r="D302" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E302" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B303" t="s">
         <v>331</v>
@@ -7267,15 +7249,15 @@
         <v>332</v>
       </c>
       <c r="D303" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E303" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B304" t="s">
         <v>331</v>
@@ -7284,15 +7266,15 @@
         <v>332</v>
       </c>
       <c r="D304" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E304" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B305" t="s">
         <v>331</v>
@@ -7301,15 +7283,15 @@
         <v>332</v>
       </c>
       <c r="D305" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E305" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B306" t="s">
         <v>331</v>
@@ -7318,15 +7300,15 @@
         <v>332</v>
       </c>
       <c r="D306" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E306" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B307" t="s">
         <v>331</v>
@@ -7335,66 +7317,66 @@
         <v>332</v>
       </c>
       <c r="D307" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E307" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B308" t="s">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="C308" t="s">
-        <v>332</v>
+        <v>348</v>
       </c>
       <c r="D308" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E308" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B309" t="s">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="C309" t="s">
-        <v>332</v>
+        <v>348</v>
       </c>
       <c r="D309" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E309" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B310" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="C310" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="D310" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E310" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B311" t="s">
         <v>331</v>
@@ -7403,15 +7385,15 @@
         <v>332</v>
       </c>
       <c r="D311" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E311" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B312" t="s">
         <v>331</v>
@@ -7420,15 +7402,15 @@
         <v>332</v>
       </c>
       <c r="D312" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E312" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B313" t="s">
         <v>331</v>
@@ -7437,15 +7419,15 @@
         <v>332</v>
       </c>
       <c r="D313" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E313" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B314" t="s">
         <v>331</v>
@@ -7454,15 +7436,15 @@
         <v>332</v>
       </c>
       <c r="D314" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E314" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B315" t="s">
         <v>331</v>
@@ -7471,15 +7453,15 @@
         <v>332</v>
       </c>
       <c r="D315" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E315" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B316" t="s">
         <v>331</v>
@@ -7488,15 +7470,15 @@
         <v>332</v>
       </c>
       <c r="D316" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E316" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B317" t="s">
         <v>331</v>
@@ -7505,15 +7487,15 @@
         <v>332</v>
       </c>
       <c r="D317" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E317" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B318" t="s">
         <v>331</v>
@@ -7522,15 +7504,15 @@
         <v>332</v>
       </c>
       <c r="D318" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E318" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B319" t="s">
         <v>331</v>
@@ -7539,15 +7521,15 @@
         <v>332</v>
       </c>
       <c r="D319" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E319" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B320" t="s">
         <v>331</v>
@@ -7556,15 +7538,15 @@
         <v>332</v>
       </c>
       <c r="D320" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E320" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B321" t="s">
         <v>331</v>
@@ -7573,15 +7555,15 @@
         <v>332</v>
       </c>
       <c r="D321" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E321" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B322" t="s">
         <v>331</v>
@@ -7590,446 +7572,446 @@
         <v>332</v>
       </c>
       <c r="D322" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E322" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B323" t="s">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="C323" t="s">
-        <v>332</v>
+        <v>348</v>
       </c>
       <c r="D323" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E323" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B324" t="s">
+        <v>347</v>
+      </c>
+      <c r="C324" t="s">
         <v>348</v>
       </c>
-      <c r="C324" t="s">
-        <v>349</v>
-      </c>
       <c r="D324" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E324" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B325" t="s">
+        <v>347</v>
+      </c>
+      <c r="C325" t="s">
         <v>348</v>
       </c>
-      <c r="C325" t="s">
-        <v>349</v>
-      </c>
       <c r="D325" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E325" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B326" t="s">
+        <v>347</v>
+      </c>
+      <c r="C326" t="s">
         <v>348</v>
       </c>
-      <c r="C326" t="s">
-        <v>349</v>
-      </c>
       <c r="D326" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E326" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B327" t="s">
+        <v>347</v>
+      </c>
+      <c r="C327" t="s">
         <v>348</v>
       </c>
-      <c r="C327" t="s">
-        <v>349</v>
-      </c>
       <c r="D327" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E327" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B328" t="s">
+        <v>347</v>
+      </c>
+      <c r="C328" t="s">
         <v>348</v>
       </c>
-      <c r="C328" t="s">
-        <v>349</v>
-      </c>
       <c r="D328" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E328" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B329" t="s">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="C329" t="s">
-        <v>332</v>
+        <v>348</v>
       </c>
       <c r="D329" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E329" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B330" t="s">
+        <v>347</v>
+      </c>
+      <c r="C330" t="s">
         <v>348</v>
       </c>
-      <c r="C330" t="s">
-        <v>349</v>
-      </c>
       <c r="D330" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E330" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B331" t="s">
+        <v>347</v>
+      </c>
+      <c r="C331" t="s">
         <v>348</v>
       </c>
-      <c r="C331" t="s">
-        <v>349</v>
-      </c>
       <c r="D331" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E331" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B332" t="s">
+        <v>347</v>
+      </c>
+      <c r="C332" t="s">
         <v>348</v>
       </c>
-      <c r="C332" t="s">
-        <v>349</v>
-      </c>
       <c r="D332" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E332" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B333" t="s">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="C333" t="s">
-        <v>332</v>
+        <v>348</v>
       </c>
       <c r="D333" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E333" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B334" t="s">
+        <v>347</v>
+      </c>
+      <c r="C334" t="s">
         <v>348</v>
       </c>
-      <c r="C334" t="s">
-        <v>349</v>
-      </c>
       <c r="D334" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E334" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B335" t="s">
+        <v>347</v>
+      </c>
+      <c r="C335" t="s">
         <v>348</v>
       </c>
-      <c r="C335" t="s">
-        <v>349</v>
-      </c>
       <c r="D335" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E335" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B336" t="s">
+        <v>347</v>
+      </c>
+      <c r="C336" t="s">
         <v>348</v>
       </c>
-      <c r="C336" t="s">
-        <v>349</v>
-      </c>
       <c r="D336" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E336" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B337" t="s">
+        <v>347</v>
+      </c>
+      <c r="C337" t="s">
         <v>348</v>
       </c>
-      <c r="C337" t="s">
-        <v>349</v>
-      </c>
       <c r="D337" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E337" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B338" t="s">
+        <v>347</v>
+      </c>
+      <c r="C338" t="s">
         <v>348</v>
       </c>
-      <c r="C338" t="s">
-        <v>349</v>
-      </c>
       <c r="D338" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E338" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B339" t="s">
+        <v>347</v>
+      </c>
+      <c r="C339" t="s">
         <v>348</v>
       </c>
-      <c r="C339" t="s">
-        <v>349</v>
-      </c>
       <c r="D339" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E339" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B340" t="s">
+        <v>347</v>
+      </c>
+      <c r="C340" t="s">
         <v>348</v>
       </c>
-      <c r="C340" t="s">
-        <v>349</v>
-      </c>
       <c r="D340" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E340" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B341" t="s">
+        <v>347</v>
+      </c>
+      <c r="C341" t="s">
         <v>348</v>
       </c>
-      <c r="C341" t="s">
-        <v>349</v>
-      </c>
       <c r="D341" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E341" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B342" t="s">
+        <v>347</v>
+      </c>
+      <c r="C342" t="s">
         <v>348</v>
       </c>
-      <c r="C342" t="s">
-        <v>349</v>
-      </c>
       <c r="D342" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E342" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B343" t="s">
+        <v>347</v>
+      </c>
+      <c r="C343" t="s">
         <v>348</v>
       </c>
-      <c r="C343" t="s">
-        <v>349</v>
-      </c>
       <c r="D343" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E343" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B344" t="s">
+        <v>347</v>
+      </c>
+      <c r="C344" t="s">
         <v>348</v>
       </c>
-      <c r="C344" t="s">
-        <v>349</v>
-      </c>
       <c r="D344" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E344" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B345" t="s">
+        <v>347</v>
+      </c>
+      <c r="C345" t="s">
         <v>348</v>
       </c>
-      <c r="C345" t="s">
-        <v>349</v>
-      </c>
       <c r="D345" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E345" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B346" t="s">
-        <v>348</v>
+        <v>387</v>
       </c>
       <c r="C346" t="s">
-        <v>349</v>
+        <v>388</v>
       </c>
       <c r="D346" t="s">
-        <v>294</v>
+        <v>389</v>
       </c>
       <c r="E346" t="s">
-        <v>295</v>
+        <v>390</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="B347" t="s">
-        <v>348</v>
+        <v>392</v>
       </c>
       <c r="C347" t="s">
-        <v>349</v>
+        <v>393</v>
       </c>
       <c r="D347" t="s">
-        <v>294</v>
+        <v>389</v>
       </c>
       <c r="E347" t="s">
-        <v>295</v>
+        <v>390</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="B348" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C348" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="D348" t="s">
         <v>389</v>
@@ -8040,13 +8022,13 @@
     </row>
     <row r="349">
       <c r="A349" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B349" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C349" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D349" t="s">
         <v>389</v>
@@ -8057,7 +8039,7 @@
     </row>
     <row r="350">
       <c r="A350" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B350" t="s">
         <v>395</v>
@@ -8074,7 +8056,7 @@
     </row>
     <row r="351">
       <c r="A351" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B351" t="s">
         <v>395</v>
@@ -8091,7 +8073,7 @@
     </row>
     <row r="352">
       <c r="A352" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B352" t="s">
         <v>395</v>
@@ -8108,7 +8090,7 @@
     </row>
     <row r="353">
       <c r="A353" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B353" t="s">
         <v>395</v>
@@ -8125,7 +8107,7 @@
     </row>
     <row r="354">
       <c r="A354" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B354" t="s">
         <v>395</v>
@@ -8142,7 +8124,7 @@
     </row>
     <row r="355">
       <c r="A355" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B355" t="s">
         <v>395</v>
@@ -8159,7 +8141,7 @@
     </row>
     <row r="356">
       <c r="A356" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B356" t="s">
         <v>395</v>
@@ -8176,7 +8158,7 @@
     </row>
     <row r="357">
       <c r="A357" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B357" t="s">
         <v>395</v>
@@ -8193,7 +8175,7 @@
     </row>
     <row r="358">
       <c r="A358" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B358" t="s">
         <v>395</v>
@@ -8210,7 +8192,7 @@
     </row>
     <row r="359">
       <c r="A359" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B359" t="s">
         <v>395</v>
@@ -8227,7 +8209,7 @@
     </row>
     <row r="360">
       <c r="A360" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B360" t="s">
         <v>395</v>
@@ -8244,7 +8226,7 @@
     </row>
     <row r="361">
       <c r="A361" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B361" t="s">
         <v>395</v>
@@ -8261,7 +8243,7 @@
     </row>
     <row r="362">
       <c r="A362" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B362" t="s">
         <v>395</v>
@@ -8278,7 +8260,7 @@
     </row>
     <row r="363">
       <c r="A363" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B363" t="s">
         <v>395</v>
@@ -8295,7 +8277,7 @@
     </row>
     <row r="364">
       <c r="A364" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B364" t="s">
         <v>395</v>
@@ -8312,7 +8294,7 @@
     </row>
     <row r="365">
       <c r="A365" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B365" t="s">
         <v>395</v>
@@ -8329,13 +8311,13 @@
     </row>
     <row r="366">
       <c r="A366" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B366" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="C366" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="D366" t="s">
         <v>389</v>
@@ -8346,13 +8328,13 @@
     </row>
     <row r="367">
       <c r="A367" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B367" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="C367" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="D367" t="s">
         <v>389</v>
@@ -8363,7 +8345,7 @@
     </row>
     <row r="368">
       <c r="A368" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B368" t="s">
         <v>387</v>
@@ -8380,7 +8362,7 @@
     </row>
     <row r="369">
       <c r="A369" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B369" t="s">
         <v>387</v>
@@ -8397,7 +8379,7 @@
     </row>
     <row r="370">
       <c r="A370" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B370" t="s">
         <v>387</v>
@@ -8414,7 +8396,7 @@
     </row>
     <row r="371">
       <c r="A371" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B371" t="s">
         <v>387</v>
@@ -8431,7 +8413,7 @@
     </row>
     <row r="372">
       <c r="A372" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B372" t="s">
         <v>387</v>
@@ -8448,7 +8430,7 @@
     </row>
     <row r="373">
       <c r="A373" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B373" t="s">
         <v>387</v>
@@ -8465,13 +8447,13 @@
     </row>
     <row r="374">
       <c r="A374" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B374" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="C374" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="D374" t="s">
         <v>389</v>
@@ -8482,7 +8464,7 @@
     </row>
     <row r="375">
       <c r="A375" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B375" t="s">
         <v>387</v>
@@ -8499,7 +8481,7 @@
     </row>
     <row r="376">
       <c r="A376" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B376" t="s">
         <v>392</v>
@@ -8516,13 +8498,13 @@
     </row>
     <row r="377">
       <c r="A377" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B377" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="C377" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="D377" t="s">
         <v>389</v>
@@ -8533,7 +8515,7 @@
     </row>
     <row r="378">
       <c r="A378" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B378" t="s">
         <v>392</v>
@@ -8550,7 +8532,7 @@
     </row>
     <row r="379">
       <c r="A379" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B379" t="s">
         <v>392</v>
@@ -8567,13 +8549,13 @@
     </row>
     <row r="380">
       <c r="A380" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B380" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="C380" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="D380" t="s">
         <v>389</v>
@@ -8584,13 +8566,13 @@
     </row>
     <row r="381">
       <c r="A381" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B381" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="C381" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="D381" t="s">
         <v>389</v>
@@ -8601,7 +8583,7 @@
     </row>
     <row r="382">
       <c r="A382" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B382" t="s">
         <v>387</v>
@@ -8618,7 +8600,7 @@
     </row>
     <row r="383">
       <c r="A383" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B383" t="s">
         <v>387</v>
@@ -8635,7 +8617,7 @@
     </row>
     <row r="384">
       <c r="A384" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B384" t="s">
         <v>387</v>
@@ -8652,7 +8634,7 @@
     </row>
     <row r="385">
       <c r="A385" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B385" t="s">
         <v>387</v>
@@ -8669,7 +8651,7 @@
     </row>
     <row r="386">
       <c r="A386" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B386" t="s">
         <v>387</v>
@@ -8686,7 +8668,7 @@
     </row>
     <row r="387">
       <c r="A387" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B387" t="s">
         <v>387</v>
@@ -8703,7 +8685,7 @@
     </row>
     <row r="388">
       <c r="A388" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B388" t="s">
         <v>387</v>
@@ -8720,7 +8702,7 @@
     </row>
     <row r="389">
       <c r="A389" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B389" t="s">
         <v>387</v>
@@ -8737,7 +8719,7 @@
     </row>
     <row r="390">
       <c r="A390" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B390" t="s">
         <v>387</v>
@@ -8754,13 +8736,13 @@
     </row>
     <row r="391">
       <c r="A391" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B391" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="C391" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="D391" t="s">
         <v>389</v>
@@ -8771,13 +8753,13 @@
     </row>
     <row r="392">
       <c r="A392" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B392" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="C392" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="D392" t="s">
         <v>389</v>
@@ -8788,7 +8770,7 @@
     </row>
     <row r="393">
       <c r="A393" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B393" t="s">
         <v>392</v>
@@ -8805,7 +8787,7 @@
     </row>
     <row r="394">
       <c r="A394" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B394" t="s">
         <v>392</v>
@@ -8822,7 +8804,7 @@
     </row>
     <row r="395">
       <c r="A395" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B395" t="s">
         <v>392</v>
@@ -8839,7 +8821,7 @@
     </row>
     <row r="396">
       <c r="A396" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B396" t="s">
         <v>392</v>
@@ -8856,7 +8838,7 @@
     </row>
     <row r="397">
       <c r="A397" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B397" t="s">
         <v>392</v>
@@ -8873,7 +8855,7 @@
     </row>
     <row r="398">
       <c r="A398" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B398" t="s">
         <v>392</v>
@@ -8890,7 +8872,7 @@
     </row>
     <row r="399">
       <c r="A399" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B399" t="s">
         <v>392</v>
@@ -8907,7 +8889,7 @@
     </row>
     <row r="400">
       <c r="A400" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B400" t="s">
         <v>392</v>
@@ -8924,7 +8906,7 @@
     </row>
     <row r="401">
       <c r="A401" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B401" t="s">
         <v>392</v>
@@ -8941,7 +8923,7 @@
     </row>
     <row r="402">
       <c r="A402" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B402" t="s">
         <v>392</v>
@@ -8958,7 +8940,7 @@
     </row>
     <row r="403">
       <c r="A403" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B403" t="s">
         <v>392</v>
@@ -8975,7 +8957,7 @@
     </row>
     <row r="404">
       <c r="A404" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B404" t="s">
         <v>392</v>
@@ -8992,7 +8974,7 @@
     </row>
     <row r="405">
       <c r="A405" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B405" t="s">
         <v>392</v>
@@ -9009,7 +8991,7 @@
     </row>
     <row r="406">
       <c r="A406" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B406" t="s">
         <v>392</v>
@@ -9026,7 +9008,7 @@
     </row>
     <row r="407">
       <c r="A407" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B407" t="s">
         <v>392</v>
@@ -9043,7 +9025,7 @@
     </row>
     <row r="408">
       <c r="A408" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B408" t="s">
         <v>392</v>
@@ -9060,7 +9042,7 @@
     </row>
     <row r="409">
       <c r="A409" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B409" t="s">
         <v>392</v>
@@ -9077,7 +9059,7 @@
     </row>
     <row r="410">
       <c r="A410" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B410" t="s">
         <v>392</v>
@@ -9094,7 +9076,7 @@
     </row>
     <row r="411">
       <c r="A411" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B411" t="s">
         <v>392</v>
@@ -9111,7 +9093,7 @@
     </row>
     <row r="412">
       <c r="A412" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B412" t="s">
         <v>392</v>
@@ -9128,7 +9110,7 @@
     </row>
     <row r="413">
       <c r="A413" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B413" t="s">
         <v>392</v>
@@ -9145,7 +9127,7 @@
     </row>
     <row r="414">
       <c r="A414" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B414" t="s">
         <v>392</v>
@@ -9162,13 +9144,13 @@
     </row>
     <row r="415">
       <c r="A415" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B415" t="s">
-        <v>392</v>
+        <v>463</v>
       </c>
       <c r="C415" t="s">
-        <v>393</v>
+        <v>464</v>
       </c>
       <c r="D415" t="s">
         <v>389</v>
@@ -9179,13 +9161,13 @@
     </row>
     <row r="416">
       <c r="A416" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B416" t="s">
-        <v>392</v>
+        <v>463</v>
       </c>
       <c r="C416" t="s">
-        <v>393</v>
+        <v>464</v>
       </c>
       <c r="D416" t="s">
         <v>389</v>
@@ -9196,7 +9178,7 @@
     </row>
     <row r="417">
       <c r="A417" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="B417" t="s">
         <v>463</v>
@@ -9213,7 +9195,7 @@
     </row>
     <row r="418">
       <c r="A418" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B418" t="s">
         <v>463</v>
@@ -9230,7 +9212,7 @@
     </row>
     <row r="419">
       <c r="A419" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B419" t="s">
         <v>463</v>
@@ -9247,7 +9229,7 @@
     </row>
     <row r="420">
       <c r="A420" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B420" t="s">
         <v>463</v>
@@ -9264,7 +9246,7 @@
     </row>
     <row r="421">
       <c r="A421" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B421" t="s">
         <v>463</v>
@@ -9281,7 +9263,7 @@
     </row>
     <row r="422">
       <c r="A422" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B422" t="s">
         <v>463</v>
@@ -9298,7 +9280,7 @@
     </row>
     <row r="423">
       <c r="A423" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B423" t="s">
         <v>463</v>
@@ -9315,7 +9297,7 @@
     </row>
     <row r="424">
       <c r="A424" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B424" t="s">
         <v>463</v>
@@ -9332,7 +9314,7 @@
     </row>
     <row r="425">
       <c r="A425" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B425" t="s">
         <v>463</v>
@@ -9349,7 +9331,7 @@
     </row>
     <row r="426">
       <c r="A426" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B426" t="s">
         <v>463</v>
@@ -9366,7 +9348,7 @@
     </row>
     <row r="427">
       <c r="A427" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B427" t="s">
         <v>463</v>
@@ -9383,7 +9365,7 @@
     </row>
     <row r="428">
       <c r="A428" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B428" t="s">
         <v>463</v>
@@ -9400,7 +9382,7 @@
     </row>
     <row r="429">
       <c r="A429" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B429" t="s">
         <v>463</v>
@@ -9417,7 +9399,7 @@
     </row>
     <row r="430">
       <c r="A430" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B430" t="s">
         <v>463</v>
@@ -9434,7 +9416,7 @@
     </row>
     <row r="431">
       <c r="A431" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B431" t="s">
         <v>463</v>
@@ -9451,7 +9433,7 @@
     </row>
     <row r="432">
       <c r="A432" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B432" t="s">
         <v>463</v>
@@ -9468,7 +9450,7 @@
     </row>
     <row r="433">
       <c r="A433" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B433" t="s">
         <v>463</v>
@@ -9485,41 +9467,41 @@
     </row>
     <row r="434">
       <c r="A434" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B434" t="s">
-        <v>463</v>
+        <v>17</v>
       </c>
       <c r="C434" t="s">
-        <v>464</v>
+        <v>18</v>
       </c>
       <c r="D434" t="s">
-        <v>389</v>
+        <v>8</v>
       </c>
       <c r="E434" t="s">
-        <v>390</v>
+        <v>9</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B435" t="s">
-        <v>463</v>
+        <v>17</v>
       </c>
       <c r="C435" t="s">
-        <v>464</v>
+        <v>18</v>
       </c>
       <c r="D435" t="s">
-        <v>389</v>
+        <v>8</v>
       </c>
       <c r="E435" t="s">
-        <v>390</v>
+        <v>9</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B436" t="s">
         <v>17</v>
@@ -9536,7 +9518,7 @@
     </row>
     <row r="437">
       <c r="A437" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B437" t="s">
         <v>17</v>
@@ -9553,13 +9535,13 @@
     </row>
     <row r="438">
       <c r="A438" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B438" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="C438" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="D438" t="s">
         <v>8</v>
@@ -9570,13 +9552,13 @@
     </row>
     <row r="439">
       <c r="A439" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B439" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="C439" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="D439" t="s">
         <v>8</v>
@@ -9587,13 +9569,13 @@
     </row>
     <row r="440">
       <c r="A440" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B440" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="C440" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="D440" t="s">
         <v>8</v>
@@ -9604,13 +9586,13 @@
     </row>
     <row r="441">
       <c r="A441" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B441" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="C441" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="D441" t="s">
         <v>8</v>
@@ -9621,13 +9603,13 @@
     </row>
     <row r="442">
       <c r="A442" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B442" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C442" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D442" t="s">
         <v>8</v>
@@ -9638,13 +9620,13 @@
     </row>
     <row r="443">
       <c r="A443" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B443" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C443" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D443" t="s">
         <v>8</v>
@@ -9655,13 +9637,13 @@
     </row>
     <row r="444">
       <c r="A444" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B444" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C444" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D444" t="s">
         <v>8</v>
@@ -9672,13 +9654,13 @@
     </row>
     <row r="445">
       <c r="A445" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B445" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C445" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D445" t="s">
         <v>8</v>
@@ -9689,13 +9671,13 @@
     </row>
     <row r="446">
       <c r="A446" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B446" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="C446" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="D446" t="s">
         <v>8</v>
@@ -9706,13 +9688,13 @@
     </row>
     <row r="447">
       <c r="A447" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B447" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="C447" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="D447" t="s">
         <v>8</v>
@@ -9723,13 +9705,13 @@
     </row>
     <row r="448">
       <c r="A448" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B448" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="C448" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="D448" t="s">
         <v>8</v>
@@ -9740,13 +9722,13 @@
     </row>
     <row r="449">
       <c r="A449" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B449" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="C449" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="D449" t="s">
         <v>8</v>
@@ -9757,13 +9739,13 @@
     </row>
     <row r="450">
       <c r="A450" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B450" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C450" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D450" t="s">
         <v>8</v>
@@ -9774,13 +9756,13 @@
     </row>
     <row r="451">
       <c r="A451" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B451" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C451" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D451" t="s">
         <v>8</v>
@@ -9791,13 +9773,13 @@
     </row>
     <row r="452">
       <c r="A452" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B452" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C452" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D452" t="s">
         <v>8</v>
@@ -9808,13 +9790,13 @@
     </row>
     <row r="453">
       <c r="A453" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B453" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C453" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D453" t="s">
         <v>8</v>
@@ -9825,13 +9807,13 @@
     </row>
     <row r="454">
       <c r="A454" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B454" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C454" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D454" t="s">
         <v>8</v>
@@ -9842,13 +9824,13 @@
     </row>
     <row r="455">
       <c r="A455" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B455" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C455" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D455" t="s">
         <v>8</v>
@@ -9859,13 +9841,13 @@
     </row>
     <row r="456">
       <c r="A456" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B456" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C456" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D456" t="s">
         <v>8</v>
@@ -9876,13 +9858,13 @@
     </row>
     <row r="457">
       <c r="A457" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B457" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C457" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D457" t="s">
         <v>8</v>
@@ -9893,13 +9875,13 @@
     </row>
     <row r="458">
       <c r="A458" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B458" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C458" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D458" t="s">
         <v>8</v>
@@ -9910,13 +9892,13 @@
     </row>
     <row r="459">
       <c r="A459" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B459" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C459" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D459" t="s">
         <v>8</v>
@@ -9927,13 +9909,13 @@
     </row>
     <row r="460">
       <c r="A460" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B460" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C460" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D460" t="s">
         <v>8</v>
@@ -9944,13 +9926,13 @@
     </row>
     <row r="461">
       <c r="A461" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B461" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C461" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D461" t="s">
         <v>8</v>
@@ -9961,13 +9943,13 @@
     </row>
     <row r="462">
       <c r="A462" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B462" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C462" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D462" t="s">
         <v>8</v>
@@ -9978,13 +9960,13 @@
     </row>
     <row r="463">
       <c r="A463" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B463" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C463" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D463" t="s">
         <v>8</v>
@@ -9995,13 +9977,13 @@
     </row>
     <row r="464">
       <c r="A464" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B464" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C464" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D464" t="s">
         <v>8</v>
@@ -10012,13 +9994,13 @@
     </row>
     <row r="465">
       <c r="A465" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B465" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="C465" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="D465" t="s">
         <v>8</v>
@@ -10029,13 +10011,13 @@
     </row>
     <row r="466">
       <c r="A466" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B466" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C466" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D466" t="s">
         <v>8</v>
@@ -10046,13 +10028,13 @@
     </row>
     <row r="467">
       <c r="A467" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B467" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C467" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D467" t="s">
         <v>8</v>
@@ -10063,13 +10045,13 @@
     </row>
     <row r="468">
       <c r="A468" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B468" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C468" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D468" t="s">
         <v>8</v>
@@ -10080,13 +10062,13 @@
     </row>
     <row r="469">
       <c r="A469" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B469" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C469" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D469" t="s">
         <v>8</v>
@@ -10097,13 +10079,13 @@
     </row>
     <row r="470">
       <c r="A470" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B470" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C470" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D470" t="s">
         <v>8</v>
@@ -10114,13 +10096,13 @@
     </row>
     <row r="471">
       <c r="A471" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B471" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C471" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D471" t="s">
         <v>8</v>
@@ -10131,13 +10113,13 @@
     </row>
     <row r="472">
       <c r="A472" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B472" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C472" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D472" t="s">
         <v>8</v>
@@ -10148,13 +10130,13 @@
     </row>
     <row r="473">
       <c r="A473" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B473" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C473" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D473" t="s">
         <v>8</v>
@@ -10165,7 +10147,7 @@
     </row>
     <row r="474">
       <c r="A474" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B474" t="s">
         <v>36</v>
@@ -10182,13 +10164,13 @@
     </row>
     <row r="475">
       <c r="A475" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B475" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="C475" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="D475" t="s">
         <v>8</v>
@@ -10199,13 +10181,13 @@
     </row>
     <row r="476">
       <c r="A476" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B476" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="C476" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="D476" t="s">
         <v>8</v>
@@ -10216,13 +10198,13 @@
     </row>
     <row r="477">
       <c r="A477" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B477" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="C477" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="D477" t="s">
         <v>8</v>
@@ -10233,13 +10215,13 @@
     </row>
     <row r="478">
       <c r="A478" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B478" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="C478" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="D478" t="s">
         <v>8</v>
@@ -10250,13 +10232,13 @@
     </row>
     <row r="479">
       <c r="A479" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B479" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="C479" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="D479" t="s">
         <v>8</v>
@@ -10267,13 +10249,13 @@
     </row>
     <row r="480">
       <c r="A480" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B480" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="C480" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="D480" t="s">
         <v>8</v>
@@ -10284,13 +10266,13 @@
     </row>
     <row r="481">
       <c r="A481" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B481" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="C481" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="D481" t="s">
         <v>8</v>
@@ -10301,13 +10283,13 @@
     </row>
     <row r="482">
       <c r="A482" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B482" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="C482" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="D482" t="s">
         <v>8</v>
@@ -10318,7 +10300,7 @@
     </row>
     <row r="483">
       <c r="A483" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B483" t="s">
         <v>36</v>
@@ -10335,7 +10317,7 @@
     </row>
     <row r="484">
       <c r="A484" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B484" t="s">
         <v>36</v>
@@ -10352,7 +10334,7 @@
     </row>
     <row r="485">
       <c r="A485" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B485" t="s">
         <v>36</v>
@@ -10369,7 +10351,7 @@
     </row>
     <row r="486">
       <c r="A486" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B486" t="s">
         <v>36</v>
@@ -10386,7 +10368,7 @@
     </row>
     <row r="487">
       <c r="A487" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B487" t="s">
         <v>36</v>
@@ -10403,7 +10385,7 @@
     </row>
     <row r="488">
       <c r="A488" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B488" t="s">
         <v>36</v>
@@ -10420,7 +10402,7 @@
     </row>
     <row r="489">
       <c r="A489" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B489" t="s">
         <v>36</v>
@@ -10437,7 +10419,7 @@
     </row>
     <row r="490">
       <c r="A490" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B490" t="s">
         <v>36</v>
@@ -10454,7 +10436,7 @@
     </row>
     <row r="491">
       <c r="A491" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B491" t="s">
         <v>36</v>
@@ -10471,7 +10453,7 @@
     </row>
     <row r="492">
       <c r="A492" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B492" t="s">
         <v>36</v>
@@ -10488,7 +10470,7 @@
     </row>
     <row r="493">
       <c r="A493" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B493" t="s">
         <v>36</v>
@@ -10505,13 +10487,13 @@
     </row>
     <row r="494">
       <c r="A494" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B494" t="s">
-        <v>36</v>
+        <v>131</v>
       </c>
       <c r="C494" t="s">
-        <v>37</v>
+        <v>132</v>
       </c>
       <c r="D494" t="s">
         <v>8</v>
@@ -10522,13 +10504,13 @@
     </row>
     <row r="495">
       <c r="A495" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B495" t="s">
-        <v>36</v>
+        <v>131</v>
       </c>
       <c r="C495" t="s">
-        <v>37</v>
+        <v>132</v>
       </c>
       <c r="D495" t="s">
         <v>8</v>
@@ -10539,13 +10521,13 @@
     </row>
     <row r="496">
       <c r="A496" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B496" t="s">
-        <v>36</v>
+        <v>131</v>
       </c>
       <c r="C496" t="s">
-        <v>37</v>
+        <v>132</v>
       </c>
       <c r="D496" t="s">
         <v>8</v>
@@ -10556,13 +10538,13 @@
     </row>
     <row r="497">
       <c r="A497" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B497" t="s">
-        <v>36</v>
+        <v>131</v>
       </c>
       <c r="C497" t="s">
-        <v>37</v>
+        <v>132</v>
       </c>
       <c r="D497" t="s">
         <v>8</v>
@@ -10573,13 +10555,13 @@
     </row>
     <row r="498">
       <c r="A498" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B498" t="s">
-        <v>36</v>
+        <v>131</v>
       </c>
       <c r="C498" t="s">
-        <v>37</v>
+        <v>132</v>
       </c>
       <c r="D498" t="s">
         <v>8</v>
@@ -10590,7 +10572,7 @@
     </row>
     <row r="499">
       <c r="A499" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B499" t="s">
         <v>36</v>
@@ -10607,7 +10589,7 @@
     </row>
     <row r="500">
       <c r="A500" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B500" t="s">
         <v>36</v>
@@ -10624,13 +10606,13 @@
     </row>
     <row r="501">
       <c r="A501" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B501" t="s">
-        <v>36</v>
+        <v>131</v>
       </c>
       <c r="C501" t="s">
-        <v>37</v>
+        <v>132</v>
       </c>
       <c r="D501" t="s">
         <v>8</v>
@@ -10641,13 +10623,13 @@
     </row>
     <row r="502">
       <c r="A502" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B502" t="s">
-        <v>36</v>
+        <v>131</v>
       </c>
       <c r="C502" t="s">
-        <v>37</v>
+        <v>132</v>
       </c>
       <c r="D502" t="s">
         <v>8</v>
@@ -10658,13 +10640,13 @@
     </row>
     <row r="503">
       <c r="A503" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B503" t="s">
+        <v>131</v>
+      </c>
+      <c r="C503" t="s">
         <v>132</v>
-      </c>
-      <c r="C503" t="s">
-        <v>133</v>
       </c>
       <c r="D503" t="s">
         <v>8</v>
@@ -10675,13 +10657,13 @@
     </row>
     <row r="504">
       <c r="A504" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B504" t="s">
+        <v>131</v>
+      </c>
+      <c r="C504" t="s">
         <v>132</v>
-      </c>
-      <c r="C504" t="s">
-        <v>133</v>
       </c>
       <c r="D504" t="s">
         <v>8</v>
@@ -10692,13 +10674,13 @@
     </row>
     <row r="505">
       <c r="A505" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B505" t="s">
+        <v>131</v>
+      </c>
+      <c r="C505" t="s">
         <v>132</v>
-      </c>
-      <c r="C505" t="s">
-        <v>133</v>
       </c>
       <c r="D505" t="s">
         <v>8</v>
@@ -10709,13 +10691,13 @@
     </row>
     <row r="506">
       <c r="A506" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B506" t="s">
+        <v>131</v>
+      </c>
+      <c r="C506" t="s">
         <v>132</v>
-      </c>
-      <c r="C506" t="s">
-        <v>133</v>
       </c>
       <c r="D506" t="s">
         <v>8</v>
@@ -10726,13 +10708,13 @@
     </row>
     <row r="507">
       <c r="A507" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B507" t="s">
+        <v>131</v>
+      </c>
+      <c r="C507" t="s">
         <v>132</v>
-      </c>
-      <c r="C507" t="s">
-        <v>133</v>
       </c>
       <c r="D507" t="s">
         <v>8</v>
@@ -10743,13 +10725,13 @@
     </row>
     <row r="508">
       <c r="A508" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B508" t="s">
-        <v>36</v>
+        <v>147</v>
       </c>
       <c r="C508" t="s">
-        <v>37</v>
+        <v>148</v>
       </c>
       <c r="D508" t="s">
         <v>8</v>
@@ -10760,13 +10742,13 @@
     </row>
     <row r="509">
       <c r="A509" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B509" t="s">
-        <v>36</v>
+        <v>147</v>
       </c>
       <c r="C509" t="s">
-        <v>37</v>
+        <v>148</v>
       </c>
       <c r="D509" t="s">
         <v>8</v>
@@ -10777,13 +10759,13 @@
     </row>
     <row r="510">
       <c r="A510" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B510" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="C510" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="D510" t="s">
         <v>8</v>
@@ -10794,13 +10776,13 @@
     </row>
     <row r="511">
       <c r="A511" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B511" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="C511" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="D511" t="s">
         <v>8</v>
@@ -10811,13 +10793,13 @@
     </row>
     <row r="512">
       <c r="A512" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B512" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="C512" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="D512" t="s">
         <v>8</v>
@@ -10828,13 +10810,13 @@
     </row>
     <row r="513">
       <c r="A513" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B513" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="C513" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="D513" t="s">
         <v>8</v>
@@ -10845,13 +10827,13 @@
     </row>
     <row r="514">
       <c r="A514" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B514" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="C514" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="D514" t="s">
         <v>8</v>
@@ -10862,13 +10844,13 @@
     </row>
     <row r="515">
       <c r="A515" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B515" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="C515" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="D515" t="s">
         <v>8</v>
@@ -10879,13 +10861,13 @@
     </row>
     <row r="516">
       <c r="A516" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B516" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="C516" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="D516" t="s">
         <v>8</v>
@@ -10896,13 +10878,13 @@
     </row>
     <row r="517">
       <c r="A517" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B517" t="s">
+        <v>147</v>
+      </c>
+      <c r="C517" t="s">
         <v>148</v>
-      </c>
-      <c r="C517" t="s">
-        <v>149</v>
       </c>
       <c r="D517" t="s">
         <v>8</v>
@@ -10913,13 +10895,13 @@
     </row>
     <row r="518">
       <c r="A518" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B518" t="s">
+        <v>147</v>
+      </c>
+      <c r="C518" t="s">
         <v>148</v>
-      </c>
-      <c r="C518" t="s">
-        <v>149</v>
       </c>
       <c r="D518" t="s">
         <v>8</v>
@@ -10930,13 +10912,13 @@
     </row>
     <row r="519">
       <c r="A519" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B519" t="s">
+        <v>147</v>
+      </c>
+      <c r="C519" t="s">
         <v>148</v>
-      </c>
-      <c r="C519" t="s">
-        <v>149</v>
       </c>
       <c r="D519" t="s">
         <v>8</v>
@@ -10947,13 +10929,13 @@
     </row>
     <row r="520">
       <c r="A520" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B520" t="s">
+        <v>147</v>
+      </c>
+      <c r="C520" t="s">
         <v>148</v>
-      </c>
-      <c r="C520" t="s">
-        <v>149</v>
       </c>
       <c r="D520" t="s">
         <v>8</v>
@@ -10964,13 +10946,13 @@
     </row>
     <row r="521">
       <c r="A521" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B521" t="s">
+        <v>147</v>
+      </c>
+      <c r="C521" t="s">
         <v>148</v>
-      </c>
-      <c r="C521" t="s">
-        <v>149</v>
       </c>
       <c r="D521" t="s">
         <v>8</v>
@@ -10981,13 +10963,13 @@
     </row>
     <row r="522">
       <c r="A522" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B522" t="s">
+        <v>147</v>
+      </c>
+      <c r="C522" t="s">
         <v>148</v>
-      </c>
-      <c r="C522" t="s">
-        <v>149</v>
       </c>
       <c r="D522" t="s">
         <v>8</v>
@@ -10998,13 +10980,13 @@
     </row>
     <row r="523">
       <c r="A523" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B523" t="s">
+        <v>147</v>
+      </c>
+      <c r="C523" t="s">
         <v>148</v>
-      </c>
-      <c r="C523" t="s">
-        <v>149</v>
       </c>
       <c r="D523" t="s">
         <v>8</v>
@@ -11015,13 +10997,13 @@
     </row>
     <row r="524">
       <c r="A524" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B524" t="s">
+        <v>147</v>
+      </c>
+      <c r="C524" t="s">
         <v>148</v>
-      </c>
-      <c r="C524" t="s">
-        <v>149</v>
       </c>
       <c r="D524" t="s">
         <v>8</v>
@@ -11032,13 +11014,13 @@
     </row>
     <row r="525">
       <c r="A525" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B525" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="C525" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="D525" t="s">
         <v>8</v>
@@ -11049,13 +11031,13 @@
     </row>
     <row r="526">
       <c r="A526" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B526" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="C526" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="D526" t="s">
         <v>8</v>
@@ -11066,13 +11048,13 @@
     </row>
     <row r="527">
       <c r="A527" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B527" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="C527" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="D527" t="s">
         <v>8</v>
@@ -11083,13 +11065,13 @@
     </row>
     <row r="528">
       <c r="A528" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B528" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="C528" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="D528" t="s">
         <v>8</v>
@@ -11100,13 +11082,13 @@
     </row>
     <row r="529">
       <c r="A529" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B529" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="C529" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="D529" t="s">
         <v>8</v>
@@ -11117,13 +11099,13 @@
     </row>
     <row r="530">
       <c r="A530" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B530" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="C530" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="D530" t="s">
         <v>8</v>
@@ -11134,13 +11116,13 @@
     </row>
     <row r="531">
       <c r="A531" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B531" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="C531" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="D531" t="s">
         <v>8</v>
@@ -11151,13 +11133,13 @@
     </row>
     <row r="532">
       <c r="A532" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B532" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="C532" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="D532" t="s">
         <v>8</v>
@@ -11168,13 +11150,13 @@
     </row>
     <row r="533">
       <c r="A533" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B533" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="C533" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="D533" t="s">
         <v>8</v>
@@ -11185,13 +11167,13 @@
     </row>
     <row r="534">
       <c r="A534" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B534" t="s">
+        <v>167</v>
+      </c>
+      <c r="C534" t="s">
         <v>168</v>
-      </c>
-      <c r="C534" t="s">
-        <v>169</v>
       </c>
       <c r="D534" t="s">
         <v>8</v>
@@ -11202,13 +11184,13 @@
     </row>
     <row r="535">
       <c r="A535" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B535" t="s">
+        <v>167</v>
+      </c>
+      <c r="C535" t="s">
         <v>168</v>
-      </c>
-      <c r="C535" t="s">
-        <v>169</v>
       </c>
       <c r="D535" t="s">
         <v>8</v>
@@ -11219,13 +11201,13 @@
     </row>
     <row r="536">
       <c r="A536" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B536" t="s">
+        <v>167</v>
+      </c>
+      <c r="C536" t="s">
         <v>168</v>
-      </c>
-      <c r="C536" t="s">
-        <v>169</v>
       </c>
       <c r="D536" t="s">
         <v>8</v>
@@ -11236,13 +11218,13 @@
     </row>
     <row r="537">
       <c r="A537" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B537" t="s">
+        <v>167</v>
+      </c>
+      <c r="C537" t="s">
         <v>168</v>
-      </c>
-      <c r="C537" t="s">
-        <v>169</v>
       </c>
       <c r="D537" t="s">
         <v>8</v>
@@ -11253,154 +11235,18 @@
     </row>
     <row r="538">
       <c r="A538" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B538" t="s">
-        <v>168</v>
+        <v>17</v>
       </c>
       <c r="C538" t="s">
-        <v>169</v>
+        <v>18</v>
       </c>
       <c r="D538" t="s">
         <v>8</v>
       </c>
       <c r="E538" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="539">
-      <c r="A539" t="s">
-        <v>586</v>
-      </c>
-      <c r="B539" t="s">
-        <v>168</v>
-      </c>
-      <c r="C539" t="s">
-        <v>169</v>
-      </c>
-      <c r="D539" t="s">
-        <v>8</v>
-      </c>
-      <c r="E539" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="540">
-      <c r="A540" t="s">
-        <v>587</v>
-      </c>
-      <c r="B540" t="s">
-        <v>168</v>
-      </c>
-      <c r="C540" t="s">
-        <v>169</v>
-      </c>
-      <c r="D540" t="s">
-        <v>8</v>
-      </c>
-      <c r="E540" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="541">
-      <c r="A541" t="s">
-        <v>588</v>
-      </c>
-      <c r="B541" t="s">
-        <v>168</v>
-      </c>
-      <c r="C541" t="s">
-        <v>169</v>
-      </c>
-      <c r="D541" t="s">
-        <v>8</v>
-      </c>
-      <c r="E541" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="542">
-      <c r="A542" t="s">
-        <v>589</v>
-      </c>
-      <c r="B542" t="s">
-        <v>168</v>
-      </c>
-      <c r="C542" t="s">
-        <v>169</v>
-      </c>
-      <c r="D542" t="s">
-        <v>8</v>
-      </c>
-      <c r="E542" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="543">
-      <c r="A543" t="s">
-        <v>590</v>
-      </c>
-      <c r="B543" t="s">
-        <v>168</v>
-      </c>
-      <c r="C543" t="s">
-        <v>169</v>
-      </c>
-      <c r="D543" t="s">
-        <v>8</v>
-      </c>
-      <c r="E543" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="544">
-      <c r="A544" t="s">
-        <v>591</v>
-      </c>
-      <c r="B544" t="s">
-        <v>168</v>
-      </c>
-      <c r="C544" t="s">
-        <v>169</v>
-      </c>
-      <c r="D544" t="s">
-        <v>8</v>
-      </c>
-      <c r="E544" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="545">
-      <c r="A545" t="s">
-        <v>592</v>
-      </c>
-      <c r="B545" t="s">
-        <v>168</v>
-      </c>
-      <c r="C545" t="s">
-        <v>169</v>
-      </c>
-      <c r="D545" t="s">
-        <v>8</v>
-      </c>
-      <c r="E545" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="546">
-      <c r="A546" t="s">
-        <v>593</v>
-      </c>
-      <c r="B546" t="s">
-        <v>168</v>
-      </c>
-      <c r="C546" t="s">
-        <v>169</v>
-      </c>
-      <c r="D546" t="s">
-        <v>8</v>
-      </c>
-      <c r="E546" t="s">
         <v>9</v>
       </c>
     </row>
